--- a/data/trans_orig/ProbViv_temp-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/ProbViv_temp-Provincia-trans_orig.xlsx
@@ -10702,12 +10702,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>14241</t>
+          <t>14928</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>37482</t>
+          <t>37371</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -10717,12 +10717,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>19,43%</t>
+          <t>20,37%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>51,15%</t>
+          <t>51,0%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -10737,12 +10737,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>10506</t>
+          <t>11202</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>25475</t>
+          <t>26987</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -10752,12 +10752,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>13,24%</t>
+          <t>14,11%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>32,1%</t>
+          <t>34,0%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -10772,12 +10772,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>28820</t>
+          <t>27824</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>55370</t>
+          <t>55893</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -10787,12 +10787,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>18,88%</t>
+          <t>18,23%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>36,27%</t>
+          <t>36,62%</t>
         </is>
       </c>
     </row>
@@ -10815,12 +10815,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>35800</t>
+          <t>35911</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>59041</t>
+          <t>58354</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -10830,12 +10830,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>48,85%</t>
+          <t>49,0%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>80,57%</t>
+          <t>79,63%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -10850,12 +10850,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>53891</t>
+          <t>52379</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>68860</t>
+          <t>68164</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -10865,12 +10865,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>67,9%</t>
+          <t>66,0%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>86,76%</t>
+          <t>85,89%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -10885,12 +10885,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>97278</t>
+          <t>96755</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>123828</t>
+          <t>124824</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -10900,12 +10900,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>63,73%</t>
+          <t>63,38%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>81,12%</t>
+          <t>81,77%</t>
         </is>
       </c>
     </row>
@@ -11045,12 +11045,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>16100</t>
+          <t>17055</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>87772</t>
+          <t>89803</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -11060,12 +11060,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>12,61%</t>
+          <t>13,36%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>68,76%</t>
+          <t>70,35%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -11080,12 +11080,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>7268</t>
+          <t>7343</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>20479</t>
+          <t>20561</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -11095,12 +11095,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>5,7%</t>
+          <t>5,75%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>16,05%</t>
+          <t>16,11%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -11115,12 +11115,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>28030</t>
+          <t>27411</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>136065</t>
+          <t>120947</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -11130,12 +11130,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>10,98%</t>
+          <t>10,74%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>53,31%</t>
+          <t>47,38%</t>
         </is>
       </c>
     </row>
@@ -11158,12 +11158,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>39882</t>
+          <t>37851</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>111554</t>
+          <t>110599</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -11173,12 +11173,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>31,24%</t>
+          <t>29,65%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>87,39%</t>
+          <t>86,64%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -11193,12 +11193,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>107117</t>
+          <t>107035</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>120328</t>
+          <t>120253</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -11208,12 +11208,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>83,95%</t>
+          <t>83,89%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>94,3%</t>
+          <t>94,25%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -11228,12 +11228,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>119185</t>
+          <t>134303</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>227220</t>
+          <t>227839</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -11243,12 +11243,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>46,69%</t>
+          <t>52,62%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>89,02%</t>
+          <t>89,26%</t>
         </is>
       </c>
     </row>
@@ -11388,12 +11388,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>18459</t>
+          <t>17974</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>29507</t>
+          <t>29698</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -11403,12 +11403,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>31,68%</t>
+          <t>30,85%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>50,64%</t>
+          <t>50,97%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -11423,12 +11423,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>18310</t>
+          <t>18229</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>30925</t>
+          <t>31017</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -11438,12 +11438,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>27,26%</t>
+          <t>27,14%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>46,05%</t>
+          <t>46,18%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -11458,12 +11458,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>39410</t>
+          <t>38705</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>57145</t>
+          <t>56433</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -11473,12 +11473,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>31,42%</t>
+          <t>30,86%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>45,56%</t>
+          <t>44,99%</t>
         </is>
       </c>
     </row>
@@ -11501,12 +11501,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>28761</t>
+          <t>28570</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>39809</t>
+          <t>40294</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -11516,12 +11516,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>49,36%</t>
+          <t>49,03%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>68,32%</t>
+          <t>69,15%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -11536,12 +11536,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>36238</t>
+          <t>36146</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>48853</t>
+          <t>48934</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -11551,12 +11551,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>53,95%</t>
+          <t>53,82%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>72,74%</t>
+          <t>72,86%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -11571,12 +11571,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>68286</t>
+          <t>68998</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>86021</t>
+          <t>86726</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -11586,12 +11586,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>54,44%</t>
+          <t>55,01%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>68,58%</t>
+          <t>69,14%</t>
         </is>
       </c>
     </row>
@@ -11731,12 +11731,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>12864</t>
+          <t>12955</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>26186</t>
+          <t>26134</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -11746,12 +11746,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>18,6%</t>
+          <t>18,74%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>37,87%</t>
+          <t>37,8%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -11766,12 +11766,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>6796</t>
+          <t>6587</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>21363</t>
+          <t>20424</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -11781,12 +11781,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>8,7%</t>
+          <t>8,43%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>27,34%</t>
+          <t>26,14%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -11801,12 +11801,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>21593</t>
+          <t>21912</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>42357</t>
+          <t>41462</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -11816,12 +11816,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>14,66%</t>
+          <t>14,88%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>28,76%</t>
+          <t>28,15%</t>
         </is>
       </c>
     </row>
@@ -11844,12 +11844,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>42958</t>
+          <t>43010</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>56280</t>
+          <t>56189</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -11859,12 +11859,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>62,13%</t>
+          <t>62,2%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>81,4%</t>
+          <t>81,26%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -11879,12 +11879,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>56771</t>
+          <t>57710</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>71338</t>
+          <t>71547</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -11894,12 +11894,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>72,66%</t>
+          <t>73,86%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>91,3%</t>
+          <t>91,57%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -11914,12 +11914,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>104921</t>
+          <t>105816</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>125685</t>
+          <t>125366</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -11929,12 +11929,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>71,24%</t>
+          <t>71,85%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>85,34%</t>
+          <t>85,12%</t>
         </is>
       </c>
     </row>
@@ -12074,12 +12074,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>5955</t>
+          <t>6057</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>13501</t>
+          <t>13702</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -12089,12 +12089,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>17,25%</t>
+          <t>17,55%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>39,12%</t>
+          <t>39,7%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -12109,12 +12109,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>7718</t>
+          <t>7905</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>17232</t>
+          <t>17223</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -12124,12 +12124,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>18,95%</t>
+          <t>19,41%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>42,32%</t>
+          <t>42,3%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -12144,12 +12144,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>16262</t>
+          <t>16308</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>28271</t>
+          <t>27659</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -12159,12 +12159,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>21,62%</t>
+          <t>21,68%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>37,58%</t>
+          <t>36,77%</t>
         </is>
       </c>
     </row>
@@ -12187,12 +12187,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>21012</t>
+          <t>20811</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>28558</t>
+          <t>28456</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -12202,12 +12202,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>60,88%</t>
+          <t>60,3%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>82,75%</t>
+          <t>82,45%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -12222,12 +12222,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>23487</t>
+          <t>23496</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>33001</t>
+          <t>32814</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -12237,12 +12237,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>57,68%</t>
+          <t>57,7%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>81,05%</t>
+          <t>80,59%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -12257,12 +12257,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>46961</t>
+          <t>47573</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>58970</t>
+          <t>58924</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -12272,12 +12272,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>62,42%</t>
+          <t>63,23%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>78,38%</t>
+          <t>78,32%</t>
         </is>
       </c>
     </row>
@@ -12417,12 +12417,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>5853</t>
+          <t>5948</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>13818</t>
+          <t>14720</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -12432,12 +12432,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>12,68%</t>
+          <t>12,88%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>29,93%</t>
+          <t>31,88%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -12452,12 +12452,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>7685</t>
+          <t>7474</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>16731</t>
+          <t>16665</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -12467,12 +12467,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>13,68%</t>
+          <t>13,3%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>29,78%</t>
+          <t>29,66%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -12487,12 +12487,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>15733</t>
+          <t>15126</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>28557</t>
+          <t>28283</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -12502,12 +12502,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>15,37%</t>
+          <t>14,78%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>27,9%</t>
+          <t>27,63%</t>
         </is>
       </c>
     </row>
@@ -12530,12 +12530,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>32349</t>
+          <t>31447</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>40314</t>
+          <t>40219</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -12545,12 +12545,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>70,07%</t>
+          <t>68,12%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>87,32%</t>
+          <t>87,12%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -12565,12 +12565,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>39455</t>
+          <t>39521</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>48501</t>
+          <t>48712</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -12580,12 +12580,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>70,22%</t>
+          <t>70,34%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>86,32%</t>
+          <t>86,7%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -12600,12 +12600,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>73796</t>
+          <t>74070</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>86620</t>
+          <t>87227</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -12615,12 +12615,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>72,1%</t>
+          <t>72,37%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>84,63%</t>
+          <t>85,22%</t>
         </is>
       </c>
     </row>
@@ -12760,12 +12760,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>39038</t>
+          <t>39402</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>58526</t>
+          <t>58928</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -12775,12 +12775,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>31,35%</t>
+          <t>31,65%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>47,01%</t>
+          <t>47,33%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -12795,12 +12795,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>47660</t>
+          <t>47934</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>73900</t>
+          <t>73576</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -12810,12 +12810,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>30,73%</t>
+          <t>30,91%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>47,66%</t>
+          <t>47,45%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -12830,12 +12830,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>93104</t>
+          <t>93272</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>125457</t>
+          <t>124663</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -12845,12 +12845,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>33,3%</t>
+          <t>33,36%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>44,87%</t>
+          <t>44,59%</t>
         </is>
       </c>
     </row>
@@ -12873,12 +12873,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>65982</t>
+          <t>65580</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>85470</t>
+          <t>85106</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -12888,12 +12888,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>52,99%</t>
+          <t>52,67%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>68,65%</t>
+          <t>68,35%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -12908,12 +12908,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>81169</t>
+          <t>81493</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>107409</t>
+          <t>107135</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -12923,12 +12923,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>52,34%</t>
+          <t>52,55%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>69,27%</t>
+          <t>69,09%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -12943,12 +12943,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>154120</t>
+          <t>154914</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>186473</t>
+          <t>186305</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -12958,12 +12958,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>55,13%</t>
+          <t>55,41%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>66,7%</t>
+          <t>66,64%</t>
         </is>
       </c>
     </row>
@@ -13103,12 +13103,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>103443</t>
+          <t>102745</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>117869</t>
+          <t>117206</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -13118,12 +13118,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>78,59%</t>
+          <t>78,06%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>89,55%</t>
+          <t>89,05%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -13138,12 +13138,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>126677</t>
+          <t>127876</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>142460</t>
+          <t>142416</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -13153,12 +13153,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>80,79%</t>
+          <t>81,56%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>90,86%</t>
+          <t>90,83%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -13173,12 +13173,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>236274</t>
+          <t>235775</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>256804</t>
+          <t>256377</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -13188,12 +13188,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>81,92%</t>
+          <t>81,75%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>89,04%</t>
+          <t>88,89%</t>
         </is>
       </c>
     </row>
@@ -13216,12 +13216,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>13750</t>
+          <t>14413</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>28176</t>
+          <t>28874</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -13231,12 +13231,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>10,45%</t>
+          <t>10,95%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>21,41%</t>
+          <t>21,94%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -13251,12 +13251,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>14335</t>
+          <t>14379</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>30118</t>
+          <t>28919</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -13266,12 +13266,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>9,14%</t>
+          <t>9,17%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>19,21%</t>
+          <t>18,44%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -13286,12 +13286,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>31610</t>
+          <t>32037</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>52140</t>
+          <t>52639</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -13301,12 +13301,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>10,96%</t>
+          <t>11,11%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>18,08%</t>
+          <t>18,25%</t>
         </is>
       </c>
     </row>
@@ -13446,12 +13446,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>257984</t>
+          <t>256029</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>342875</t>
+          <t>338376</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -13461,12 +13461,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>38,79%</t>
+          <t>38,49%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>51,55%</t>
+          <t>50,87%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -13481,12 +13481,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>259269</t>
+          <t>260623</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>310694</t>
+          <t>312103</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -13496,12 +13496,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>34,07%</t>
+          <t>34,25%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>40,83%</t>
+          <t>41,01%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -13516,12 +13516,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>532894</t>
+          <t>535925</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>629449</t>
+          <t>633137</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -13531,12 +13531,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>37,37%</t>
+          <t>37,58%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>44,14%</t>
+          <t>44,39%</t>
         </is>
       </c>
     </row>
@@ -13559,12 +13559,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>322281</t>
+          <t>326780</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>407172</t>
+          <t>409127</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -13574,12 +13574,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>48,45%</t>
+          <t>49,13%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>61,21%</t>
+          <t>61,51%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -13594,12 +13594,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>450334</t>
+          <t>448925</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>501759</t>
+          <t>500405</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -13609,12 +13609,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>59,17%</t>
+          <t>58,99%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>65,93%</t>
+          <t>65,75%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -13629,12 +13629,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>796735</t>
+          <t>793047</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>893290</t>
+          <t>890259</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -13644,12 +13644,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>55,86%</t>
+          <t>55,61%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>62,63%</t>
+          <t>62,42%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/ProbViv_temp-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/ProbViv_temp-Provincia-trans_orig.xlsx
@@ -544,7 +544,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -555,7 +555,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -836,47 +836,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>72</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>51164</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>77</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>47707</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>72</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>51164</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
@@ -949,57 +949,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>72</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>51164</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>51164</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>51164</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>77</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>47707</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>47707</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>47707</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>72</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>51164</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>51164</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>51164</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1179,47 +1179,47 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>97</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>64934</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>104</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>67887</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>97</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>64934</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
@@ -1292,57 +1292,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>97</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>64934</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>64934</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>64934</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>104</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>67887</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>67887</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>67887</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>97</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>64934</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>64934</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>64934</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1522,47 +1522,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>109</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>67902</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>89</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>64697</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>109</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>67902</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
@@ -1635,57 +1635,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>109</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>67902</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>67902</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>67902</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>89</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>64697</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>64697</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>64697</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>109</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>67902</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>67902</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>67902</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1865,47 +1865,47 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>107</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>73516</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>100</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>66054</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>107</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>73516</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
@@ -1978,57 +1978,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>107</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>73516</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>73516</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>73516</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>100</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>66054</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>66054</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>66054</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>107</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>73516</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>73516</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>73516</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2208,47 +2208,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>11399</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>14</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>9541</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>11399</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
@@ -2321,57 +2321,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>11399</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>11399</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>11399</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>14</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>9541</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
         <is>
           <t>9541</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="M18" s="2" t="inlineStr">
         <is>
           <t>9541</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>11399</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>11399</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>11399</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2551,47 +2551,47 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>82</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>52271</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
           <t>68</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="K20" s="2" t="inlineStr">
         <is>
           <t>46659</t>
-        </is>
-      </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t>82</t>
-        </is>
-      </c>
-      <c r="K20" s="2" t="inlineStr">
-        <is>
-          <t>52271</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
@@ -2664,57 +2664,57 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
+          <t>82</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>52271</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>52271</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>52271</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
           <t>68</t>
         </is>
       </c>
-      <c r="D21" s="2" t="inlineStr">
+      <c r="K21" s="2" t="inlineStr">
         <is>
           <t>46659</t>
         </is>
       </c>
-      <c r="E21" s="2" t="inlineStr">
+      <c r="L21" s="2" t="inlineStr">
         <is>
           <t>46659</t>
         </is>
       </c>
-      <c r="F21" s="2" t="inlineStr">
+      <c r="M21" s="2" t="inlineStr">
         <is>
           <t>46659</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J21" s="2" t="inlineStr">
-        <is>
-          <t>82</t>
-        </is>
-      </c>
-      <c r="K21" s="2" t="inlineStr">
-        <is>
-          <t>52271</t>
-        </is>
-      </c>
-      <c r="L21" s="2" t="inlineStr">
-        <is>
-          <t>52271</t>
-        </is>
-      </c>
-      <c r="M21" s="2" t="inlineStr">
-        <is>
-          <t>52271</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2899,42 +2899,42 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
+          <t>110786</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
+          <t>160</t>
+        </is>
+      </c>
+      <c r="K23" s="2" t="inlineStr">
+        <is>
           <t>110646</t>
-        </is>
-      </c>
-      <c r="E23" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J23" s="2" t="inlineStr">
-        <is>
-          <t>160</t>
-        </is>
-      </c>
-      <c r="K23" s="2" t="inlineStr">
-        <is>
-          <t>110786</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
@@ -3012,52 +3012,52 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
+          <t>110786</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>110786</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>110786</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
+          <t>160</t>
+        </is>
+      </c>
+      <c r="K24" s="2" t="inlineStr">
+        <is>
           <t>110646</t>
         </is>
       </c>
-      <c r="E24" s="2" t="inlineStr">
+      <c r="L24" s="2" t="inlineStr">
         <is>
           <t>110646</t>
         </is>
       </c>
-      <c r="F24" s="2" t="inlineStr">
+      <c r="M24" s="2" t="inlineStr">
         <is>
           <t>110646</t>
-        </is>
-      </c>
-      <c r="G24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J24" s="2" t="inlineStr">
-        <is>
-          <t>160</t>
-        </is>
-      </c>
-      <c r="K24" s="2" t="inlineStr">
-        <is>
-          <t>110786</t>
-        </is>
-      </c>
-      <c r="L24" s="2" t="inlineStr">
-        <is>
-          <t>110786</t>
-        </is>
-      </c>
-      <c r="M24" s="2" t="inlineStr">
-        <is>
-          <t>110786</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3237,47 +3237,47 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
+          <t>149</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>96577</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr">
+        <is>
           <t>134</t>
         </is>
       </c>
-      <c r="D26" s="2" t="inlineStr">
+      <c r="K26" s="2" t="inlineStr">
         <is>
           <t>90167</t>
-        </is>
-      </c>
-      <c r="E26" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F26" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G26" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H26" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I26" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J26" s="2" t="inlineStr">
-        <is>
-          <t>149</t>
-        </is>
-      </c>
-      <c r="K26" s="2" t="inlineStr">
-        <is>
-          <t>96577</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
@@ -3350,57 +3350,57 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
+          <t>149</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>96577</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>96577</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>96577</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J27" s="2" t="inlineStr">
+        <is>
           <t>134</t>
         </is>
       </c>
-      <c r="D27" s="2" t="inlineStr">
+      <c r="K27" s="2" t="inlineStr">
         <is>
           <t>90167</t>
         </is>
       </c>
-      <c r="E27" s="2" t="inlineStr">
+      <c r="L27" s="2" t="inlineStr">
         <is>
           <t>90167</t>
         </is>
       </c>
-      <c r="F27" s="2" t="inlineStr">
+      <c r="M27" s="2" t="inlineStr">
         <is>
           <t>90167</t>
-        </is>
-      </c>
-      <c r="G27" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H27" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I27" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J27" s="2" t="inlineStr">
-        <is>
-          <t>149</t>
-        </is>
-      </c>
-      <c r="K27" s="2" t="inlineStr">
-        <is>
-          <t>96577</t>
-        </is>
-      </c>
-      <c r="L27" s="2" t="inlineStr">
-        <is>
-          <t>96577</t>
-        </is>
-      </c>
-      <c r="M27" s="2" t="inlineStr">
-        <is>
-          <t>96577</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3580,47 +3580,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
+          <t>792</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>528549</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H29" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I29" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J29" s="2" t="inlineStr">
+        <is>
           <t>746</t>
         </is>
       </c>
-      <c r="D29" s="2" t="inlineStr">
+      <c r="K29" s="2" t="inlineStr">
         <is>
           <t>503359</t>
-        </is>
-      </c>
-      <c r="E29" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F29" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G29" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H29" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I29" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J29" s="2" t="inlineStr">
-        <is>
-          <t>792</t>
-        </is>
-      </c>
-      <c r="K29" s="2" t="inlineStr">
-        <is>
-          <t>528549</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
@@ -3693,57 +3693,57 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
+          <t>792</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>528549</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>528549</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t>528549</t>
+        </is>
+      </c>
+      <c r="G30" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H30" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I30" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J30" s="2" t="inlineStr">
+        <is>
           <t>746</t>
         </is>
       </c>
-      <c r="D30" s="2" t="inlineStr">
+      <c r="K30" s="2" t="inlineStr">
         <is>
           <t>503359</t>
         </is>
       </c>
-      <c r="E30" s="2" t="inlineStr">
+      <c r="L30" s="2" t="inlineStr">
         <is>
           <t>503359</t>
         </is>
       </c>
-      <c r="F30" s="2" t="inlineStr">
+      <c r="M30" s="2" t="inlineStr">
         <is>
           <t>503359</t>
-        </is>
-      </c>
-      <c r="G30" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H30" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I30" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J30" s="2" t="inlineStr">
-        <is>
-          <t>792</t>
-        </is>
-      </c>
-      <c r="K30" s="2" t="inlineStr">
-        <is>
-          <t>528549</t>
-        </is>
-      </c>
-      <c r="L30" s="2" t="inlineStr">
-        <is>
-          <t>528549</t>
-        </is>
-      </c>
-      <c r="M30" s="2" t="inlineStr">
-        <is>
-          <t>528549</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3867,7 +3867,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -3878,7 +3878,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -4159,47 +4159,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>53</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>38080</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>42</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>25357</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>53</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>38080</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
@@ -4272,57 +4272,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>53</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>38080</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>38080</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>38080</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>42</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>25357</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>25357</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>25357</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>53</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>38080</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>38080</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>38080</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -4502,47 +4502,47 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>89</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>58886</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>79</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>54386</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>89</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>58886</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
@@ -4615,57 +4615,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>89</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>58886</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>58886</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>58886</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>79</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>54386</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>54386</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>54386</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>89</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>58886</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>58886</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>58886</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -4845,47 +4845,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>86</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>59934</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>72</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>52713</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>86</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>59934</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
@@ -4958,57 +4958,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>86</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>59934</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>59934</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>59934</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>72</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>52713</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>52713</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>52713</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>86</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>59934</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>59934</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>59934</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -5188,47 +5188,47 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>74</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>55472</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>72</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>49680</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>74</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>55472</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
@@ -5301,57 +5301,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>74</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>55472</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>55472</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>55472</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>72</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>49680</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>49680</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>49680</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>74</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>55472</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>55472</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>55472</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -5531,47 +5531,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>24630</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>24</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>18043</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>34</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>24630</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
@@ -5644,57 +5644,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>24630</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>24630</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>24630</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>24</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>18043</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
         <is>
           <t>18043</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="M18" s="2" t="inlineStr">
         <is>
           <t>18043</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>34</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>24630</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>24630</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>24630</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -5874,47 +5874,47 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>69</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>49533</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
           <t>63</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="K20" s="2" t="inlineStr">
         <is>
           <t>44542</t>
-        </is>
-      </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t>69</t>
-        </is>
-      </c>
-      <c r="K20" s="2" t="inlineStr">
-        <is>
-          <t>49533</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
@@ -5987,57 +5987,57 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
+          <t>69</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>49533</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>49533</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>49533</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
           <t>63</t>
         </is>
       </c>
-      <c r="D21" s="2" t="inlineStr">
+      <c r="K21" s="2" t="inlineStr">
         <is>
           <t>44542</t>
         </is>
       </c>
-      <c r="E21" s="2" t="inlineStr">
+      <c r="L21" s="2" t="inlineStr">
         <is>
           <t>44542</t>
         </is>
       </c>
-      <c r="F21" s="2" t="inlineStr">
+      <c r="M21" s="2" t="inlineStr">
         <is>
           <t>44542</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J21" s="2" t="inlineStr">
-        <is>
-          <t>69</t>
-        </is>
-      </c>
-      <c r="K21" s="2" t="inlineStr">
-        <is>
-          <t>49533</t>
-        </is>
-      </c>
-      <c r="L21" s="2" t="inlineStr">
-        <is>
-          <t>49533</t>
-        </is>
-      </c>
-      <c r="M21" s="2" t="inlineStr">
-        <is>
-          <t>49533</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -6217,47 +6217,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
+          <t>174</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>121777</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
           <t>163</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
+      <c r="K23" s="2" t="inlineStr">
         <is>
           <t>116704</t>
-        </is>
-      </c>
-      <c r="E23" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J23" s="2" t="inlineStr">
-        <is>
-          <t>174</t>
-        </is>
-      </c>
-      <c r="K23" s="2" t="inlineStr">
-        <is>
-          <t>121777</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
@@ -6330,57 +6330,57 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
+          <t>174</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>121777</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>121777</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>121777</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
           <t>163</t>
         </is>
       </c>
-      <c r="D24" s="2" t="inlineStr">
+      <c r="K24" s="2" t="inlineStr">
         <is>
           <t>116704</t>
         </is>
       </c>
-      <c r="E24" s="2" t="inlineStr">
+      <c r="L24" s="2" t="inlineStr">
         <is>
           <t>116704</t>
         </is>
       </c>
-      <c r="F24" s="2" t="inlineStr">
+      <c r="M24" s="2" t="inlineStr">
         <is>
           <t>116704</t>
-        </is>
-      </c>
-      <c r="G24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J24" s="2" t="inlineStr">
-        <is>
-          <t>174</t>
-        </is>
-      </c>
-      <c r="K24" s="2" t="inlineStr">
-        <is>
-          <t>121777</t>
-        </is>
-      </c>
-      <c r="L24" s="2" t="inlineStr">
-        <is>
-          <t>121777</t>
-        </is>
-      </c>
-      <c r="M24" s="2" t="inlineStr">
-        <is>
-          <t>121777</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -6560,47 +6560,47 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
+          <t>190</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>130468</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr">
+        <is>
           <t>172</t>
         </is>
       </c>
-      <c r="D26" s="2" t="inlineStr">
+      <c r="K26" s="2" t="inlineStr">
         <is>
           <t>115539</t>
-        </is>
-      </c>
-      <c r="E26" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F26" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G26" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H26" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I26" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J26" s="2" t="inlineStr">
-        <is>
-          <t>190</t>
-        </is>
-      </c>
-      <c r="K26" s="2" t="inlineStr">
-        <is>
-          <t>130468</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
@@ -6673,57 +6673,57 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
+          <t>190</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>130468</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>130468</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>130468</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J27" s="2" t="inlineStr">
+        <is>
           <t>172</t>
         </is>
       </c>
-      <c r="D27" s="2" t="inlineStr">
+      <c r="K27" s="2" t="inlineStr">
         <is>
           <t>115539</t>
         </is>
       </c>
-      <c r="E27" s="2" t="inlineStr">
+      <c r="L27" s="2" t="inlineStr">
         <is>
           <t>115539</t>
         </is>
       </c>
-      <c r="F27" s="2" t="inlineStr">
+      <c r="M27" s="2" t="inlineStr">
         <is>
           <t>115539</t>
-        </is>
-      </c>
-      <c r="G27" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H27" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I27" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J27" s="2" t="inlineStr">
-        <is>
-          <t>190</t>
-        </is>
-      </c>
-      <c r="K27" s="2" t="inlineStr">
-        <is>
-          <t>130468</t>
-        </is>
-      </c>
-      <c r="L27" s="2" t="inlineStr">
-        <is>
-          <t>130468</t>
-        </is>
-      </c>
-      <c r="M27" s="2" t="inlineStr">
-        <is>
-          <t>130468</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -6903,47 +6903,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
+          <t>769</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>538781</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H29" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I29" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J29" s="2" t="inlineStr">
+        <is>
           <t>687</t>
         </is>
       </c>
-      <c r="D29" s="2" t="inlineStr">
+      <c r="K29" s="2" t="inlineStr">
         <is>
           <t>476965</t>
-        </is>
-      </c>
-      <c r="E29" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F29" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G29" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H29" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I29" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J29" s="2" t="inlineStr">
-        <is>
-          <t>769</t>
-        </is>
-      </c>
-      <c r="K29" s="2" t="inlineStr">
-        <is>
-          <t>538781</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
@@ -7016,57 +7016,57 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
+          <t>769</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>538781</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>538781</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t>538781</t>
+        </is>
+      </c>
+      <c r="G30" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H30" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I30" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J30" s="2" t="inlineStr">
+        <is>
           <t>687</t>
         </is>
       </c>
-      <c r="D30" s="2" t="inlineStr">
+      <c r="K30" s="2" t="inlineStr">
         <is>
           <t>476965</t>
         </is>
       </c>
-      <c r="E30" s="2" t="inlineStr">
+      <c r="L30" s="2" t="inlineStr">
         <is>
           <t>476965</t>
         </is>
       </c>
-      <c r="F30" s="2" t="inlineStr">
+      <c r="M30" s="2" t="inlineStr">
         <is>
           <t>476965</t>
-        </is>
-      </c>
-      <c r="G30" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H30" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I30" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J30" s="2" t="inlineStr">
-        <is>
-          <t>769</t>
-        </is>
-      </c>
-      <c r="K30" s="2" t="inlineStr">
-        <is>
-          <t>538781</t>
-        </is>
-      </c>
-      <c r="L30" s="2" t="inlineStr">
-        <is>
-          <t>538781</t>
-        </is>
-      </c>
-      <c r="M30" s="2" t="inlineStr">
-        <is>
-          <t>538781</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -7190,7 +7190,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -7201,7 +7201,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -7482,47 +7482,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>74</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>51994</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>73</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>45386</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>74</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>51994</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
@@ -7595,57 +7595,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>74</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>51994</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>51994</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>51994</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>73</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>45386</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>45386</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>45386</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>74</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>51994</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>51994</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>51994</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -7825,47 +7825,47 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>117</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>79995</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>106</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>70702</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>117</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>79995</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
@@ -7938,57 +7938,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>117</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>79995</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>79995</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>79995</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>106</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>70702</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>70702</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>70702</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>117</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>79995</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>79995</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>79995</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -8168,47 +8168,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>93</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>66177</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>76</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>58113</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>93</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>66177</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
@@ -8281,57 +8281,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>93</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>66177</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>66177</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>66177</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>76</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>58113</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>58113</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>58113</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>93</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>66177</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>66177</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>66177</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -8516,42 +8516,42 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
+          <t>47650</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>64</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
           <t>45113</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>64</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>47650</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
@@ -8629,52 +8629,52 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
+          <t>47650</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>47650</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>47650</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>64</t>
+        </is>
+      </c>
+      <c r="K15" s="2" t="inlineStr">
+        <is>
           <t>45113</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>45113</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>45113</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>64</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>47650</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>47650</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>47650</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -8854,47 +8854,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>53</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>35516</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>48</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>32375</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>53</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>35516</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
@@ -8967,57 +8967,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>53</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>35516</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>35516</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>35516</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>48</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>32375</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
         <is>
           <t>32375</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="M18" s="2" t="inlineStr">
         <is>
           <t>32375</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>53</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>35516</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>35516</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>35516</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -9197,47 +9197,47 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>43</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>31356</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
           <t>41</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="K20" s="2" t="inlineStr">
         <is>
           <t>27283</t>
-        </is>
-      </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t>43</t>
-        </is>
-      </c>
-      <c r="K20" s="2" t="inlineStr">
-        <is>
-          <t>31356</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
@@ -9310,57 +9310,57 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
+          <t>43</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>31356</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>31356</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>31356</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
           <t>41</t>
         </is>
       </c>
-      <c r="D21" s="2" t="inlineStr">
+      <c r="K21" s="2" t="inlineStr">
         <is>
           <t>27283</t>
         </is>
       </c>
-      <c r="E21" s="2" t="inlineStr">
+      <c r="L21" s="2" t="inlineStr">
         <is>
           <t>27283</t>
         </is>
       </c>
-      <c r="F21" s="2" t="inlineStr">
+      <c r="M21" s="2" t="inlineStr">
         <is>
           <t>27283</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J21" s="2" t="inlineStr">
-        <is>
-          <t>43</t>
-        </is>
-      </c>
-      <c r="K21" s="2" t="inlineStr">
-        <is>
-          <t>31356</t>
-        </is>
-      </c>
-      <c r="L21" s="2" t="inlineStr">
-        <is>
-          <t>31356</t>
-        </is>
-      </c>
-      <c r="M21" s="2" t="inlineStr">
-        <is>
-          <t>31356</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -9540,47 +9540,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
+          <t>172</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>119123</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
           <t>176</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
+      <c r="K23" s="2" t="inlineStr">
         <is>
           <t>116765</t>
-        </is>
-      </c>
-      <c r="E23" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J23" s="2" t="inlineStr">
-        <is>
-          <t>172</t>
-        </is>
-      </c>
-      <c r="K23" s="2" t="inlineStr">
-        <is>
-          <t>119123</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
@@ -9653,57 +9653,57 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
+          <t>172</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>119123</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>119123</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>119123</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
           <t>176</t>
         </is>
       </c>
-      <c r="D24" s="2" t="inlineStr">
+      <c r="K24" s="2" t="inlineStr">
         <is>
           <t>116765</t>
         </is>
       </c>
-      <c r="E24" s="2" t="inlineStr">
+      <c r="L24" s="2" t="inlineStr">
         <is>
           <t>116765</t>
         </is>
       </c>
-      <c r="F24" s="2" t="inlineStr">
+      <c r="M24" s="2" t="inlineStr">
         <is>
           <t>116765</t>
-        </is>
-      </c>
-      <c r="G24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J24" s="2" t="inlineStr">
-        <is>
-          <t>172</t>
-        </is>
-      </c>
-      <c r="K24" s="2" t="inlineStr">
-        <is>
-          <t>119123</t>
-        </is>
-      </c>
-      <c r="L24" s="2" t="inlineStr">
-        <is>
-          <t>119123</t>
-        </is>
-      </c>
-      <c r="M24" s="2" t="inlineStr">
-        <is>
-          <t>119123</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -9883,47 +9883,47 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
+          <t>209</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>139223</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr">
+        <is>
           <t>206</t>
         </is>
       </c>
-      <c r="D26" s="2" t="inlineStr">
+      <c r="K26" s="2" t="inlineStr">
         <is>
           <t>129653</t>
-        </is>
-      </c>
-      <c r="E26" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F26" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G26" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H26" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I26" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J26" s="2" t="inlineStr">
-        <is>
-          <t>209</t>
-        </is>
-      </c>
-      <c r="K26" s="2" t="inlineStr">
-        <is>
-          <t>139223</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
@@ -9996,57 +9996,57 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
+          <t>209</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>139223</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>139223</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>139223</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J27" s="2" t="inlineStr">
+        <is>
           <t>206</t>
         </is>
       </c>
-      <c r="D27" s="2" t="inlineStr">
+      <c r="K27" s="2" t="inlineStr">
         <is>
           <t>129653</t>
         </is>
       </c>
-      <c r="E27" s="2" t="inlineStr">
+      <c r="L27" s="2" t="inlineStr">
         <is>
           <t>129653</t>
         </is>
       </c>
-      <c r="F27" s="2" t="inlineStr">
+      <c r="M27" s="2" t="inlineStr">
         <is>
           <t>129653</t>
-        </is>
-      </c>
-      <c r="G27" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H27" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I27" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J27" s="2" t="inlineStr">
-        <is>
-          <t>209</t>
-        </is>
-      </c>
-      <c r="K27" s="2" t="inlineStr">
-        <is>
-          <t>139223</t>
-        </is>
-      </c>
-      <c r="L27" s="2" t="inlineStr">
-        <is>
-          <t>139223</t>
-        </is>
-      </c>
-      <c r="M27" s="2" t="inlineStr">
-        <is>
-          <t>139223</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -10226,47 +10226,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
+          <t>825</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>571033</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H29" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I29" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J29" s="2" t="inlineStr">
+        <is>
           <t>790</t>
         </is>
       </c>
-      <c r="D29" s="2" t="inlineStr">
+      <c r="K29" s="2" t="inlineStr">
         <is>
           <t>525390</t>
-        </is>
-      </c>
-      <c r="E29" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F29" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G29" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H29" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I29" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J29" s="2" t="inlineStr">
-        <is>
-          <t>825</t>
-        </is>
-      </c>
-      <c r="K29" s="2" t="inlineStr">
-        <is>
-          <t>571033</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
@@ -10339,57 +10339,57 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
+          <t>825</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>571033</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>571033</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t>571033</t>
+        </is>
+      </c>
+      <c r="G30" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H30" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I30" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J30" s="2" t="inlineStr">
+        <is>
           <t>790</t>
         </is>
       </c>
-      <c r="D30" s="2" t="inlineStr">
+      <c r="K30" s="2" t="inlineStr">
         <is>
           <t>525390</t>
         </is>
       </c>
-      <c r="E30" s="2" t="inlineStr">
+      <c r="L30" s="2" t="inlineStr">
         <is>
           <t>525390</t>
         </is>
       </c>
-      <c r="F30" s="2" t="inlineStr">
+      <c r="M30" s="2" t="inlineStr">
         <is>
           <t>525390</t>
-        </is>
-      </c>
-      <c r="G30" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H30" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I30" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J30" s="2" t="inlineStr">
-        <is>
-          <t>825</t>
-        </is>
-      </c>
-      <c r="K30" s="2" t="inlineStr">
-        <is>
-          <t>571033</t>
-        </is>
-      </c>
-      <c r="L30" s="2" t="inlineStr">
-        <is>
-          <t>571033</t>
-        </is>
-      </c>
-      <c r="M30" s="2" t="inlineStr">
-        <is>
-          <t>571033</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -10513,7 +10513,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -10524,7 +10524,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -10692,72 +10692,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>10771</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>6556</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>16650</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>16,79%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>10,22%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>25,96%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>21</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>22819</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>14928</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>37371</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>31,14%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>20,37%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>51,0%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>17186</t>
+          <t>12628</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>11202</t>
+          <t>8096</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>26987</t>
+          <t>17746</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>21,65%</t>
+          <t>22,36%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>14,11%</t>
+          <t>14,33%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>34,0%</t>
+          <t>31,42%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -10767,32 +10767,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>40005</t>
+          <t>23399</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>27824</t>
+          <t>17656</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>55893</t>
+          <t>30797</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>26,21%</t>
+          <t>19,4%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>18,23%</t>
+          <t>14,64%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>36,62%</t>
+          <t>25,53%</t>
         </is>
       </c>
     </row>
@@ -10805,72 +10805,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>84</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>53374</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>47495</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>57589</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>83,21%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>74,04%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>89,78%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>75</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>50463</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>35911</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>58354</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>68,86%</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>49,0%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>79,63%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>84</t>
-        </is>
-      </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>62180</t>
+          <t>43853</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>52379</t>
+          <t>38735</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>68164</t>
+          <t>48385</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>78,35%</t>
+          <t>77,64%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>66,0%</t>
+          <t>68,58%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>85,89%</t>
+          <t>85,67%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -10880,32 +10880,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>112643</t>
+          <t>97227</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>96755</t>
+          <t>89829</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>124824</t>
+          <t>102970</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>73,79%</t>
+          <t>80,6%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>63,38%</t>
+          <t>74,47%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>81,77%</t>
+          <t>85,36%</t>
         </is>
       </c>
     </row>
@@ -10918,57 +10918,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>102</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>64145</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>64145</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>64145</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>96</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>73282</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>73282</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>73282</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>102</t>
-        </is>
-      </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>79366</t>
+          <t>56481</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>79366</t>
+          <t>56481</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>79366</t>
+          <t>56481</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -10993,17 +10993,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>152648</t>
+          <t>120626</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>152648</t>
+          <t>120626</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>152648</t>
+          <t>120626</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -11035,72 +11035,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>11432</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>6107</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>18195</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>9,87%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>5,27%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>15,71%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>19</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>42526</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>17055</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>89803</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>33,31%</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>13,36%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>70,35%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>12577</t>
+          <t>16044</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>7343</t>
+          <t>10126</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>20561</t>
+          <t>26211</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>9,86%</t>
+          <t>15,82%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>5,75%</t>
+          <t>9,99%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>16,11%</t>
+          <t>25,85%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -11110,32 +11110,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>55103</t>
+          <t>27476</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>27411</t>
+          <t>19325</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>120947</t>
+          <t>38791</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>21,59%</t>
+          <t>12,65%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>10,74%</t>
+          <t>8,9%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>47,38%</t>
+          <t>17,86%</t>
         </is>
       </c>
     </row>
@@ -11148,72 +11148,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>139</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>104403</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>97640</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>109728</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>90,13%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>84,29%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>94,73%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>123</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>85128</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>37851</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>110599</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>66,69%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>29,65%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>86,64%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>139</t>
-        </is>
-      </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>115019</t>
+          <t>85351</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>107035</t>
+          <t>75184</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>120253</t>
+          <t>91269</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>90,14%</t>
+          <t>84,18%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>83,89%</t>
+          <t>74,15%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>94,25%</t>
+          <t>90,01%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -11223,32 +11223,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>200147</t>
+          <t>189755</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>134303</t>
+          <t>178440</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>227839</t>
+          <t>197906</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>78,41%</t>
+          <t>87,35%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>52,62%</t>
+          <t>82,14%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>89,26%</t>
+          <t>91,1%</t>
         </is>
       </c>
     </row>
@@ -11261,57 +11261,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>156</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>115835</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>115835</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>115835</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>142</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>127654</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>127654</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>127654</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>156</t>
-        </is>
-      </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>127596</t>
+          <t>101395</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>127596</t>
+          <t>101395</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>127596</t>
+          <t>101395</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -11336,17 +11336,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>255250</t>
+          <t>217231</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>255250</t>
+          <t>217231</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>255250</t>
+          <t>217231</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -11378,72 +11378,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>21502</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>15661</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>27290</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>36,21%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>26,38%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>45,96%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>39</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>24015</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>17974</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>29698</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>41,22%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>30,85%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>50,97%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>37</t>
-        </is>
-      </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>24190</t>
+          <t>23428</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>18229</t>
+          <t>17645</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>31017</t>
+          <t>29241</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>36,02%</t>
+          <t>41,42%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>27,14%</t>
+          <t>31,2%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>46,18%</t>
+          <t>51,7%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -11453,32 +11453,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>48205</t>
+          <t>44931</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>38705</t>
+          <t>36768</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>56433</t>
+          <t>52286</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>38,43%</t>
+          <t>38,75%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>30,86%</t>
+          <t>31,71%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>44,99%</t>
+          <t>45,1%</t>
         </is>
       </c>
     </row>
@@ -11491,72 +11491,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>64</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>37875</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>32087</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>43716</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>63,79%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>54,04%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>73,62%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>58</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>34253</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>28570</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>40294</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>58,78%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>49,03%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>69,15%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>64</t>
-        </is>
-      </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>42973</t>
+          <t>33130</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>36146</t>
+          <t>27317</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>48934</t>
+          <t>38913</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>63,98%</t>
+          <t>58,58%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>53,82%</t>
+          <t>48,3%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>72,86%</t>
+          <t>68,8%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -11566,32 +11566,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>77226</t>
+          <t>71005</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>68998</t>
+          <t>63650</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>86726</t>
+          <t>79168</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>61,57%</t>
+          <t>61,25%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>55,01%</t>
+          <t>54,9%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>69,14%</t>
+          <t>68,29%</t>
         </is>
       </c>
     </row>
@@ -11604,57 +11604,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>101</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>59377</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>59377</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>59377</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>97</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>58268</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>58268</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>58268</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>101</t>
-        </is>
-      </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>67163</t>
+          <t>56558</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>67163</t>
+          <t>56558</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>67163</t>
+          <t>56558</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -11679,17 +11679,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>125431</t>
+          <t>115936</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>125431</t>
+          <t>115936</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>125431</t>
+          <t>115936</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -11721,72 +11721,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>11504</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>6300</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>19879</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>15,94%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>8,73%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>27,55%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>25</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>19147</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>12955</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>26134</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>27,69%</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>18,74%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>37,8%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>12503</t>
+          <t>18518</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>6587</t>
+          <t>12373</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>20424</t>
+          <t>26279</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>16,0%</t>
+          <t>26,54%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>8,43%</t>
+          <t>17,73%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>26,14%</t>
+          <t>37,67%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -11796,32 +11796,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>31650</t>
+          <t>30022</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>21912</t>
+          <t>19747</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>41462</t>
+          <t>39267</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>21,49%</t>
+          <t>21,15%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>14,88%</t>
+          <t>13,91%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>28,15%</t>
+          <t>27,67%</t>
         </is>
       </c>
     </row>
@@ -11834,72 +11834,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>53</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>60658</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>52283</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>65862</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>84,06%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>72,45%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>91,27%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>68</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>49997</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>43010</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>56189</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>72,31%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>62,2%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>81,26%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>53</t>
-        </is>
-      </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>65631</t>
+          <t>51250</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>57710</t>
+          <t>43489</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>71547</t>
+          <t>57395</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>84,0%</t>
+          <t>73,46%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>73,86%</t>
+          <t>62,33%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>91,57%</t>
+          <t>82,27%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -11909,32 +11909,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>115628</t>
+          <t>111908</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>105816</t>
+          <t>102663</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>125366</t>
+          <t>122183</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>78,51%</t>
+          <t>78,85%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>71,85%</t>
+          <t>72,33%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>85,12%</t>
+          <t>86,09%</t>
         </is>
       </c>
     </row>
@@ -11947,57 +11947,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>68</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>72162</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>72162</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>72162</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>93</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>69144</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>69144</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>69144</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>68</t>
-        </is>
-      </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>78134</t>
+          <t>69768</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>78134</t>
+          <t>69768</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>78134</t>
+          <t>69768</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -12022,17 +12022,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>147278</t>
+          <t>141930</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>147278</t>
+          <t>141930</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>147278</t>
+          <t>141930</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -12064,72 +12064,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>10710</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>6901</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>15640</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>27,06%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>17,44%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>39,52%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>18</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>9465</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>6057</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>13702</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>27,42%</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>17,55%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>39,7%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>11992</t>
+          <t>9966</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>7905</t>
+          <t>6199</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>17223</t>
+          <t>14314</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>29,45%</t>
+          <t>27,99%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>19,41%</t>
+          <t>17,41%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>42,3%</t>
+          <t>40,2%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -12139,32 +12139,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>21457</t>
+          <t>20675</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>16308</t>
+          <t>15395</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>27659</t>
+          <t>26214</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>28,52%</t>
+          <t>27,5%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>21,68%</t>
+          <t>20,48%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>36,77%</t>
+          <t>34,86%</t>
         </is>
       </c>
     </row>
@@ -12177,72 +12177,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>28869</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>23939</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>32678</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>72,94%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>60,48%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>82,56%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>50</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>25048</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>20811</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>28456</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>72,58%</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>60,3%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>82,45%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>52</t>
-        </is>
-      </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>28727</t>
+          <t>25642</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>23496</t>
+          <t>21294</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>32814</t>
+          <t>29409</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>70,55%</t>
+          <t>72,01%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>57,7%</t>
+          <t>59,8%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>80,59%</t>
+          <t>82,59%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -12252,32 +12252,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>53775</t>
+          <t>54512</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>47573</t>
+          <t>48973</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>58924</t>
+          <t>59792</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>71,48%</t>
+          <t>72,5%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>63,23%</t>
+          <t>65,14%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>78,32%</t>
+          <t>79,52%</t>
         </is>
       </c>
     </row>
@@ -12290,57 +12290,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>71</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>39579</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>39579</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>39579</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>68</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>34513</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>34513</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>34513</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>71</t>
-        </is>
-      </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>40719</t>
+          <t>35608</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>40719</t>
+          <t>35608</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>40719</t>
+          <t>35608</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -12365,17 +12365,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>75232</t>
+          <t>75187</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>75232</t>
+          <t>75187</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>75232</t>
+          <t>75187</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -12407,72 +12407,72 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>10420</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>6808</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>15225</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>21,29%</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>13,91%</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>31,11%</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
           <t>17</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
-        <is>
-          <t>9673</t>
-        </is>
-      </c>
-      <c r="E19" s="2" t="inlineStr">
-        <is>
-          <t>5948</t>
-        </is>
-      </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>14720</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
-        <is>
-          <t>20,95%</t>
-        </is>
-      </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>12,88%</t>
-        </is>
-      </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>31,88%</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>11702</t>
+          <t>9694</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>7474</t>
+          <t>5862</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>16665</t>
+          <t>14407</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>20,83%</t>
+          <t>21,18%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>13,3%</t>
+          <t>12,81%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>29,66%</t>
+          <t>31,48%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -12482,32 +12482,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>21375</t>
+          <t>20114</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>15126</t>
+          <t>14874</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>28283</t>
+          <t>25772</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>20,88%</t>
+          <t>21,24%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>14,78%</t>
+          <t>15,71%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>27,63%</t>
+          <t>27,21%</t>
         </is>
       </c>
     </row>
@@ -12520,72 +12520,72 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>71</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>38522</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>33717</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>42134</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>78,71%</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>68,89%</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>86,09%</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
           <t>62</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
-        <is>
-          <t>36494</t>
-        </is>
-      </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>31447</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>40219</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>79,05%</t>
-        </is>
-      </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>68,12%</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>87,12%</t>
-        </is>
-      </c>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t>71</t>
-        </is>
-      </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>44484</t>
+          <t>36072</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>39521</t>
+          <t>31359</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>48712</t>
+          <t>39904</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>79,17%</t>
+          <t>78,82%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>70,34%</t>
+          <t>68,52%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>86,7%</t>
+          <t>87,19%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -12595,32 +12595,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>80978</t>
+          <t>74594</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>74070</t>
+          <t>68936</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>87227</t>
+          <t>79834</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>79,12%</t>
+          <t>78,76%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>72,37%</t>
+          <t>72,79%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>85,22%</t>
+          <t>84,29%</t>
         </is>
       </c>
     </row>
@@ -12633,57 +12633,57 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
+          <t>93</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>48942</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>48942</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>48942</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
           <t>79</t>
         </is>
       </c>
-      <c r="D21" s="2" t="inlineStr">
-        <is>
-          <t>46167</t>
-        </is>
-      </c>
-      <c r="E21" s="2" t="inlineStr">
-        <is>
-          <t>46167</t>
-        </is>
-      </c>
-      <c r="F21" s="2" t="inlineStr">
-        <is>
-          <t>46167</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J21" s="2" t="inlineStr">
-        <is>
-          <t>93</t>
-        </is>
-      </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>56186</t>
+          <t>45766</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>56186</t>
+          <t>45766</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>56186</t>
+          <t>45766</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -12708,17 +12708,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>102353</t>
+          <t>94708</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>102353</t>
+          <t>94708</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>102353</t>
+          <t>94708</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -12750,72 +12750,72 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>71</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>55321</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>44599</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>65438</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>39,4%</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>31,76%</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>46,6%</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
           <t>66</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
-        <is>
-          <t>47854</t>
-        </is>
-      </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>39402</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>58928</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
-        <is>
-          <t>38,43%</t>
-        </is>
-      </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>31,65%</t>
-        </is>
-      </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>47,33%</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>71</t>
-        </is>
-      </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>60662</t>
+          <t>46830</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>47934</t>
+          <t>37649</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>73576</t>
+          <t>56324</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>39,12%</t>
+          <t>38,22%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>30,91%</t>
+          <t>30,73%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>47,45%</t>
+          <t>45,97%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -12825,32 +12825,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>108517</t>
+          <t>102150</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>93272</t>
+          <t>86944</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>124663</t>
+          <t>115643</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>38,81%</t>
+          <t>38,85%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>33,36%</t>
+          <t>33,07%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>44,59%</t>
+          <t>43,98%</t>
         </is>
       </c>
     </row>
@@ -12863,72 +12863,72 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
+          <t>106</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>85090</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>74973</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>95812</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>60,6%</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>53,4%</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>68,24%</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
           <t>110</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
-        <is>
-          <t>76654</t>
-        </is>
-      </c>
-      <c r="E23" s="2" t="inlineStr">
-        <is>
-          <t>65580</t>
-        </is>
-      </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>85106</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
-        <is>
-          <t>61,57%</t>
-        </is>
-      </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>52,67%</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>68,35%</t>
-        </is>
-      </c>
-      <c r="J23" s="2" t="inlineStr">
-        <is>
-          <t>106</t>
-        </is>
-      </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>94407</t>
+          <t>75699</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>81493</t>
+          <t>66205</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>107135</t>
+          <t>84880</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>60,88%</t>
+          <t>61,78%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>52,55%</t>
+          <t>54,03%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>69,09%</t>
+          <t>69,27%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -12938,32 +12938,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>171060</t>
+          <t>160790</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>154914</t>
+          <t>147297</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>186305</t>
+          <t>175996</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>61,19%</t>
+          <t>61,15%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>55,41%</t>
+          <t>56,02%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>66,64%</t>
+          <t>66,93%</t>
         </is>
       </c>
     </row>
@@ -12976,57 +12976,57 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
+          <t>177</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>140411</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>140411</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>140411</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
           <t>176</t>
         </is>
       </c>
-      <c r="D24" s="2" t="inlineStr">
-        <is>
-          <t>124508</t>
-        </is>
-      </c>
-      <c r="E24" s="2" t="inlineStr">
-        <is>
-          <t>124508</t>
-        </is>
-      </c>
-      <c r="F24" s="2" t="inlineStr">
-        <is>
-          <t>124508</t>
-        </is>
-      </c>
-      <c r="G24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J24" s="2" t="inlineStr">
-        <is>
-          <t>177</t>
-        </is>
-      </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>155069</t>
+          <t>122529</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>155069</t>
+          <t>122529</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>155069</t>
+          <t>122529</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -13051,17 +13051,17 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>279577</t>
+          <t>262940</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>279577</t>
+          <t>262940</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>279577</t>
+          <t>262940</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -13093,72 +13093,72 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
+          <t>179</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>138344</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>129906</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>145559</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>86,78%</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>81,49%</t>
+        </is>
+      </c>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>91,31%</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="inlineStr">
+        <is>
           <t>163</t>
         </is>
       </c>
-      <c r="D25" s="2" t="inlineStr">
-        <is>
-          <t>111063</t>
-        </is>
-      </c>
-      <c r="E25" s="2" t="inlineStr">
-        <is>
-          <t>102745</t>
-        </is>
-      </c>
-      <c r="F25" s="2" t="inlineStr">
-        <is>
-          <t>117206</t>
-        </is>
-      </c>
-      <c r="G25" s="2" t="inlineStr">
-        <is>
-          <t>84,38%</t>
-        </is>
-      </c>
-      <c r="H25" s="2" t="inlineStr">
-        <is>
-          <t>78,06%</t>
-        </is>
-      </c>
-      <c r="I25" s="2" t="inlineStr">
-        <is>
-          <t>89,05%</t>
-        </is>
-      </c>
-      <c r="J25" s="2" t="inlineStr">
-        <is>
-          <t>179</t>
-        </is>
-      </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>135977</t>
+          <t>118179</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>127876</t>
+          <t>107159</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>142416</t>
+          <t>125268</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>86,72%</t>
+          <t>84,11%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>81,56%</t>
+          <t>76,27%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>90,83%</t>
+          <t>89,16%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -13168,32 +13168,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>247040</t>
+          <t>256523</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>235775</t>
+          <t>245262</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>256377</t>
+          <t>267375</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>85,65%</t>
+          <t>85,53%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>81,75%</t>
+          <t>81,78%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>88,89%</t>
+          <t>89,15%</t>
         </is>
       </c>
     </row>
@@ -13206,72 +13206,72 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>21077</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>13862</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>29515</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>13,22%</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>8,69%</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>18,51%</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr">
+        <is>
           <t>28</t>
         </is>
       </c>
-      <c r="D26" s="2" t="inlineStr">
-        <is>
-          <t>20556</t>
-        </is>
-      </c>
-      <c r="E26" s="2" t="inlineStr">
-        <is>
-          <t>14413</t>
-        </is>
-      </c>
-      <c r="F26" s="2" t="inlineStr">
-        <is>
-          <t>28874</t>
-        </is>
-      </c>
-      <c r="G26" s="2" t="inlineStr">
-        <is>
-          <t>15,62%</t>
-        </is>
-      </c>
-      <c r="H26" s="2" t="inlineStr">
-        <is>
-          <t>10,95%</t>
-        </is>
-      </c>
-      <c r="I26" s="2" t="inlineStr">
-        <is>
-          <t>21,94%</t>
-        </is>
-      </c>
-      <c r="J26" s="2" t="inlineStr">
-        <is>
-          <t>29</t>
-        </is>
-      </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>20818</t>
+          <t>22318</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>14379</t>
+          <t>15229</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>28919</t>
+          <t>33338</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>13,28%</t>
+          <t>15,89%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>9,17%</t>
+          <t>10,84%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>18,44%</t>
+          <t>23,73%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -13281,32 +13281,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>41374</t>
+          <t>43395</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>32037</t>
+          <t>32543</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>52639</t>
+          <t>54656</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>14,35%</t>
+          <t>14,47%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>11,11%</t>
+          <t>10,85%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>18,25%</t>
+          <t>18,22%</t>
         </is>
       </c>
     </row>
@@ -13319,57 +13319,57 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
+          <t>208</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>159421</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>159421</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>159421</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J27" s="2" t="inlineStr">
+        <is>
           <t>191</t>
         </is>
       </c>
-      <c r="D27" s="2" t="inlineStr">
-        <is>
-          <t>131619</t>
-        </is>
-      </c>
-      <c r="E27" s="2" t="inlineStr">
-        <is>
-          <t>131619</t>
-        </is>
-      </c>
-      <c r="F27" s="2" t="inlineStr">
-        <is>
-          <t>131619</t>
-        </is>
-      </c>
-      <c r="G27" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H27" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I27" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J27" s="2" t="inlineStr">
-        <is>
-          <t>208</t>
-        </is>
-      </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>156795</t>
+          <t>140497</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>156795</t>
+          <t>140497</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>156795</t>
+          <t>140497</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -13394,17 +13394,17 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>288414</t>
+          <t>299918</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>288414</t>
+          <t>299918</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>288414</t>
+          <t>299918</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -13436,72 +13436,72 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
+          <t>378</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>270003</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>243222</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>292631</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
+          <t>38,58%</t>
+        </is>
+      </c>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t>34,75%</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="inlineStr">
+        <is>
+          <t>41,81%</t>
+        </is>
+      </c>
+      <c r="J28" s="2" t="inlineStr">
+        <is>
           <t>368</t>
         </is>
       </c>
-      <c r="D28" s="2" t="inlineStr">
-        <is>
-          <t>286563</t>
-        </is>
-      </c>
-      <c r="E28" s="2" t="inlineStr">
-        <is>
-          <t>256029</t>
-        </is>
-      </c>
-      <c r="F28" s="2" t="inlineStr">
-        <is>
-          <t>338376</t>
-        </is>
-      </c>
-      <c r="G28" s="2" t="inlineStr">
-        <is>
-          <t>43,08%</t>
-        </is>
-      </c>
-      <c r="H28" s="2" t="inlineStr">
-        <is>
-          <t>38,49%</t>
-        </is>
-      </c>
-      <c r="I28" s="2" t="inlineStr">
-        <is>
-          <t>50,87%</t>
-        </is>
-      </c>
-      <c r="J28" s="2" t="inlineStr">
-        <is>
-          <t>378</t>
-        </is>
-      </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>286789</t>
+          <t>255288</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>260623</t>
+          <t>234289</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>312103</t>
+          <t>274834</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t>37,68%</t>
+          <t>40,61%</t>
         </is>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>34,25%</t>
+          <t>37,27%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>41,01%</t>
+          <t>43,72%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -13511,32 +13511,32 @@
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>573352</t>
+          <t>525290</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>535925</t>
+          <t>493395</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>633137</t>
+          <t>557944</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
         <is>
-          <t>40,2%</t>
+          <t>39,54%</t>
         </is>
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>37,58%</t>
+          <t>37,14%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>44,39%</t>
+          <t>42,0%</t>
         </is>
       </c>
     </row>
@@ -13549,72 +13549,72 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
+          <t>598</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>429869</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>407241</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>456650</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="inlineStr">
+        <is>
+          <t>61,42%</t>
+        </is>
+      </c>
+      <c r="H29" s="2" t="inlineStr">
+        <is>
+          <t>58,19%</t>
+        </is>
+      </c>
+      <c r="I29" s="2" t="inlineStr">
+        <is>
+          <t>65,25%</t>
+        </is>
+      </c>
+      <c r="J29" s="2" t="inlineStr">
+        <is>
           <t>574</t>
         </is>
       </c>
-      <c r="D29" s="2" t="inlineStr">
-        <is>
-          <t>378593</t>
-        </is>
-      </c>
-      <c r="E29" s="2" t="inlineStr">
-        <is>
-          <t>326780</t>
-        </is>
-      </c>
-      <c r="F29" s="2" t="inlineStr">
-        <is>
-          <t>409127</t>
-        </is>
-      </c>
-      <c r="G29" s="2" t="inlineStr">
-        <is>
-          <t>56,92%</t>
-        </is>
-      </c>
-      <c r="H29" s="2" t="inlineStr">
-        <is>
-          <t>49,13%</t>
-        </is>
-      </c>
-      <c r="I29" s="2" t="inlineStr">
-        <is>
-          <t>61,51%</t>
-        </is>
-      </c>
-      <c r="J29" s="2" t="inlineStr">
-        <is>
-          <t>598</t>
-        </is>
-      </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>474239</t>
+          <t>373315</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>448925</t>
+          <t>353769</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>500405</t>
+          <t>394314</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>62,32%</t>
+          <t>59,39%</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>58,99%</t>
+          <t>56,28%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>65,75%</t>
+          <t>62,73%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -13624,32 +13624,32 @@
       </c>
       <c r="R29" s="2" t="inlineStr">
         <is>
-          <t>852832</t>
+          <t>803185</t>
         </is>
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>793047</t>
+          <t>770531</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>890259</t>
+          <t>835080</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
         <is>
-          <t>59,8%</t>
+          <t>60,46%</t>
         </is>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>55,61%</t>
+          <t>58,0%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>62,42%</t>
+          <t>62,86%</t>
         </is>
       </c>
     </row>
@@ -13662,57 +13662,57 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
+          <t>976</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>699872</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>699872</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t>699872</t>
+        </is>
+      </c>
+      <c r="G30" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H30" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I30" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J30" s="2" t="inlineStr">
+        <is>
           <t>942</t>
         </is>
       </c>
-      <c r="D30" s="2" t="inlineStr">
-        <is>
-          <t>665156</t>
-        </is>
-      </c>
-      <c r="E30" s="2" t="inlineStr">
-        <is>
-          <t>665156</t>
-        </is>
-      </c>
-      <c r="F30" s="2" t="inlineStr">
-        <is>
-          <t>665156</t>
-        </is>
-      </c>
-      <c r="G30" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H30" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I30" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J30" s="2" t="inlineStr">
-        <is>
-          <t>976</t>
-        </is>
-      </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>761028</t>
+          <t>628603</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>761028</t>
+          <t>628603</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>761028</t>
+          <t>628603</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -13737,17 +13737,17 @@
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t>1426184</t>
+          <t>1328475</t>
         </is>
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>1426184</t>
+          <t>1328475</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>1426184</t>
+          <t>1328475</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
